--- a/backend/tests/fixtures/synthetic/vendor_export.xlsx
+++ b/backend/tests/fixtures/synthetic/vendor_export.xlsx
@@ -489,7 +489,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ada@example.com</t>
+          <t>ada@acme.example</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>grace@example.org</t>
+          <t>grace@globex.example</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
